--- a/data/comparison.xlsx
+++ b/data/comparison.xlsx
@@ -13,20 +13,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="172">
+  <si>
+    <t>Требование</t>
+  </si>
   <si>
     <t>Кошка или собака: выбор питомца для городской семьи</t>
   </si>
   <si>
+    <t>Методика и правила чтения</t>
+  </si>
+  <si>
     <t>Демонстрационная сравнительная матрица. Выводы описывают типичные бытовые сценарии; возраст, здоровье, характер и прошлый опыт конкретного животного могут изменить оценку.</t>
   </si>
   <si>
-    <t>Требование</t>
-  </si>
-  <si>
-    <t>Методика и правила чтения</t>
-  </si>
-  <si>
     <t>Кошка</t>
   </si>
   <si>
@@ -45,16 +45,16 @@
     <t>Определение</t>
   </si>
   <si>
-    <t>Как трактовать</t>
-  </si>
-  <si>
-    <t>Пример</t>
+    <t>Просто</t>
+  </si>
+  <si>
+    <t>Сценарий обычно совместим с потребностями животного без сложной дополнительной организации.</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Просто</t>
+    <t>Есть затруднения</t>
   </si>
   <si>
     <t>Критерий</t>
@@ -66,6 +66,9 @@
     <t>Перевод на технический язык</t>
   </si>
   <si>
+    <t>Сценарий реалистичен, если владелец заранее выполняет конкретные условия.</t>
+  </si>
+  <si>
     <t>Что ищем в источниках</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t>Возможности кошки</t>
   </si>
   <si>
-    <t>Сценарий обычно совместим с потребностями животного без сложной дополнительной организации.</t>
-  </si>
-  <si>
     <t>Ограничения кошки</t>
   </si>
   <si>
@@ -87,49 +87,43 @@
     <t>Источники кошки</t>
   </si>
   <si>
-    <t>Базовый уход всё равно обязателен; статус не означает, что усилий не потребуется.</t>
-  </si>
-  <si>
     <t>Статус собаки</t>
   </si>
   <si>
     <t>Возможности собаки</t>
   </si>
   <si>
-    <t>Спокойный взрослый питомец в подходящем доме</t>
-  </si>
-  <si>
     <t>Ограничения собаки</t>
   </si>
   <si>
+    <t>Очень сложно</t>
+  </si>
+  <si>
     <t>Ссылка на проверку собаки</t>
   </si>
   <si>
+    <t>Без регулярной помощи, времени или специальных договорённостей сценарий рискован.</t>
+  </si>
+  <si>
     <t>Источники собаки</t>
   </si>
   <si>
     <t>Вывод для будущего владельца</t>
   </si>
   <si>
-    <t>Есть затруднения</t>
-  </si>
-  <si>
     <t>p_01</t>
   </si>
   <si>
-    <t>Сценарий реалистичен, если владелец заранее выполняет конкретные условия.</t>
-  </si>
-  <si>
     <t>Время в одиночестве</t>
   </si>
   <si>
-    <t>Условия перечислены в ограничениях и должны быть проверены до выбора животного.</t>
-  </si>
-  <si>
-    <t>Кошка в небольшой квартире с вертикальным пространством</t>
+    <t>Зависит от животного</t>
   </si>
   <si>
     <t>Какой питомец лучше подходит человеку, который в будни надолго уходит из дома?</t>
+  </si>
+  <si>
+    <t>Вид питомца не даёт надёжного ответа: решают возраст, здоровье, характер и прошлый опыт.</t>
   </si>
   <si>
     <t>Сопоставить допустимую продолжительность одиночества, частоту обязательного ухода и необходимость присутствия человека в течение дня.</t>
@@ -142,40 +136,58 @@
 5. Нужен ли дневной помощник.</t>
   </si>
   <si>
-    <t>Очень сложно</t>
-  </si>
-  <si>
-    <t>Без регулярной помощи, времени или специальных договорённостей сценарий рискован.</t>
-  </si>
-  <si>
-    <t>Нужно заранее подтвердить ресурсы, а не рассчитывать решить вопрос после появления питомца.</t>
-  </si>
-  <si>
-    <t>Собака при полном рабочем дне и без дневной прогулки</t>
-  </si>
-  <si>
-    <t>Зависит от животного</t>
-  </si>
-  <si>
-    <t>Вид питомца не даёт надёжного ответа: решают возраст, здоровье, характер и прошлый опыт.</t>
-  </si>
-  <si>
-    <t>Нужна оценка конкретного животного и условий семьи.</t>
-  </si>
-  <si>
-    <t>Совместимость с детьми или другим питомцем</t>
+    <t>Правило</t>
+  </si>
+  <si>
+    <t>Применение в этой матрице</t>
+  </si>
+  <si>
+    <t>Единица сравнения</t>
+  </si>
+  <si>
+    <t>Сравнивается не абстрактная популярность кошек и собак, а пригодность для конкретных городских бытовых сценариев.</t>
+  </si>
+  <si>
+    <t>Варианты</t>
+  </si>
+  <si>
+    <t>Вариант A — кошка. Вариант B — собака. Названия колонок повторяют структуру рабочей сравнительной матрицы.</t>
+  </si>
+  <si>
+    <t>Источники</t>
+  </si>
+  <si>
+    <t>Использованы открытые рекомендации благотворительных организаций по защите животных. Полные URL приведены в строках матрицы.</t>
+  </si>
+  <si>
+    <t>Обобщения</t>
+  </si>
+  <si>
+    <t>Формулировки описывают типичные условия, но не приписывают одинаковое поведение всем кошкам или всем собакам.</t>
+  </si>
+  <si>
+    <t>Нет общего победителя</t>
+  </si>
+  <si>
+    <t>Вывод по каждому критерию зависит от образа жизни владельца. Итоговое приложение должно помогать выбирать условия, а не объявлять один вид лучше другого.</t>
+  </si>
+  <si>
+    <t>Обновление данных</t>
+  </si>
+  <si>
+    <t>Приложение должно читать все заполненные строки. Число критериев может меняться без переписывания интерфейса.</t>
+  </si>
+  <si>
+    <t>Совместимость с рабочей версией</t>
+  </si>
+  <si>
+    <t>Сохраняются 16 логических полей: требование, пять полей варианта A, пять полей варианта B и итоговый вывод. При подключении рабочей таблицы меняются данные и названия вариантов, а не структура экранов.</t>
   </si>
   <si>
     <t>Взрослая кошка обычно не требует прогулок по расписанию. При наличии воды, корма, чистого лотка, безопасной среды и занятий рабочий день владельца организовать проще.</t>
   </si>
   <si>
-    <t>Правило</t>
-  </si>
-  <si>
     <t>Кошка не должна регулярно оставаться без проверки на длительные сроки. Молодым, пожилым и больным животным нужен более частый контроль. Скука и нехватка контакта остаются риском.</t>
-  </si>
-  <si>
-    <t>Применение в этой матрице</t>
   </si>
   <si>
     <t>www.cat.mur</t>
@@ -185,52 +197,19 @@
 Общие рекомендации: www.cat.mur_01</t>
   </si>
   <si>
-    <t>Единица сравнения</t>
-  </si>
-  <si>
-    <t>Сравнивается не абстрактная популярность кошек и собак, а пригодность для конкретных городских бытовых сценариев.</t>
-  </si>
-  <si>
-    <t>Варианты</t>
-  </si>
-  <si>
     <t>Взрослая собака может оставаться одна часть дня, если её постепенно приучили, заранее выгуляли и обеспечили безопасное место.</t>
   </si>
   <si>
-    <t>Вариант A — кошка. Вариант B — собака. Названия колонок повторяют структуру рабочей сравнительной матрицы.</t>
-  </si>
-  <si>
-    <t>Источники</t>
-  </si>
-  <si>
     <t>Нужны регулярные прогулки, туалет и контакт. Щенок или собака с тревогой разлуки не подходят для длинного рабочего дня без выгульщика, родственника или дневного присмотра.</t>
   </si>
   <si>
-    <t>Использованы открытые рекомендации благотворительных организаций по защите животных. Полные URL приведены в строках матрицы.</t>
-  </si>
-  <si>
     <t>www.dog.av</t>
   </si>
   <si>
     <t>Общие рекомендации по собакам: www.dog.av_01</t>
   </si>
   <si>
-    <t>Обобщения</t>
-  </si>
-  <si>
-    <t>Формулировки описывают типичные условия, но не приписывают одинаковое поведение всем кошкам или всем собакам.</t>
-  </si>
-  <si>
     <t xml:space="preserve">При полном рабочем дне кошка обычно проще организационно. Собака возможна, только если заранее решён вопрос дневной прогулки и присмотра в щенячьем возрасте. </t>
-  </si>
-  <si>
-    <t>Нет общего победителя</t>
-  </si>
-  <si>
-    <t>Вывод по каждому критерию зависит от образа жизни владельца. Итоговое приложение должно помогать выбирать условия, а не объявлять один вид лучше другого.</t>
-  </si>
-  <si>
-    <t>Обновление данных</t>
   </si>
   <si>
     <t>p_02</t>
@@ -251,19 +230,10 @@
 4. Последствия недостатка активности.</t>
   </si>
   <si>
-    <t>Приложение должно читать все заполненные строки. Число критериев может меняться без переписывания интерфейса.</t>
-  </si>
-  <si>
-    <t>Совместимость с рабочей версией</t>
-  </si>
-  <si>
     <t>Активность можно организовать дома: игры, лазание, когтеточки, поиск корма. Нет обязательных уличных выходов по часам.</t>
   </si>
   <si>
     <t>Домашняя кошка всё равно нуждается в ежедневных играх и вертикальном пространстве. Молодые и очень активные животные требуют заметно больше времени.</t>
-  </si>
-  <si>
-    <t>Сохраняются 16 логических полей: требование, пять полей варианта A, пять полей варианта B и итоговый вывод. При подключении рабочей таблицы меняются данные и названия вариантов, а не структура экранов.</t>
   </si>
   <si>
     <t>Дом, игры и вертикальное пространство: www.cat.mur_01</t>
@@ -613,13 +583,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Carlito"/>
     </font>
     <font>
       <b/>
@@ -741,20 +711,6 @@
   <borders count="11">
     <border/>
     <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-    </border>
-    <border>
       <right style="thin">
         <color rgb="FFD9E1E8"/>
       </right>
@@ -775,10 +731,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9E1E8"/>
+        <color rgb="FFFFFFFF"/>
       </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FFD9E1E8"/>
+        <color rgb="FFFFFFFF"/>
       </bottom>
     </border>
     <border>
@@ -807,17 +769,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD9E1E8"/>
-      </left>
-      <top style="thin">
-        <color rgb="FFD9E1E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1E8"/>
-      </bottom>
-    </border>
-    <border>
       <right style="thin">
         <color rgb="FFD9E1E8"/>
       </right>
@@ -835,6 +786,25 @@
       <top style="thin">
         <color rgb="FFD9E1E8"/>
       </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1E8"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FFD9E1E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1E8"/>
+      </left>
+      <top style="thin">
+        <color rgb="FFD9E1E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1E8"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -873,118 +843,118 @@
     <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="5" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="13" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="6" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="13" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1219,13 +1189,13 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2242,7 +2212,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>4</v>
@@ -2255,694 +2225,694 @@
       </c>
     </row>
     <row r="2" ht="55.5" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="N2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" s="29" t="s">
+      <c r="L3" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="O3" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="O3" s="29" t="s">
+    </row>
+    <row r="4" ht="116.25" customHeight="1">
+      <c r="A4" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="P3" s="30" t="s">
+      <c r="B4" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="4" ht="116.25" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="E4" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="K4" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="M4" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="N4" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="P4" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="34" t="s">
+    </row>
+    <row r="5" ht="116.25" customHeight="1">
+      <c r="A5" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="36" t="s">
+      <c r="G5" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="K4" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="38" t="s">
+      <c r="H5" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="38" t="s">
+      <c r="I5" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O4" s="38" t="s">
+      <c r="K5" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="P4" s="39" t="s">
+      <c r="M5" s="38" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" ht="116.25" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="N5" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="P5" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="33" t="s">
+    </row>
+    <row r="6" ht="116.25" customHeight="1">
+      <c r="A6" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="B6" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="C6" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="36" t="s">
+      <c r="D6" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="E6" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="36" t="s">
+      <c r="F6" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="K5" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="38" t="s">
+      <c r="H6" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="I6" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="N5" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O5" s="38" t="s">
+      <c r="K6" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="P5" s="39" t="s">
+      <c r="M6" s="38" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="6" ht="116.25" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="N6" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="P6" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="33" t="s">
+    </row>
+    <row r="7" ht="116.25" customHeight="1">
+      <c r="A7" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="B7" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="36" t="s">
+      <c r="D7" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="E7" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="36" t="s">
+      <c r="F7" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="H7" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="M7" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="N7" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="P7" s="39" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" ht="116.25" customHeight="1">
+      <c r="A8" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="M8" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="N8" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="P8" s="39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" ht="116.25" customHeight="1">
+      <c r="A9" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="M6" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="N6" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O6" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="P6" s="39" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" ht="116.25" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="K7" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="M7" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="N7" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O7" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="P7" s="39" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" ht="116.25" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="36" t="s">
+      <c r="G9" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="K8" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="38" t="s">
+      <c r="H9" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="M8" s="38" t="s">
+      <c r="I9" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O8" s="38" t="s">
+      <c r="K9" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="P8" s="39" t="s">
+      <c r="M9" s="38" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="9" ht="116.25" customHeight="1">
-      <c r="A9" s="31" t="s">
+      <c r="N9" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="P9" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="33" t="s">
+    </row>
+    <row r="10" ht="116.25" customHeight="1">
+      <c r="A10" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="B10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="36" t="s">
+      <c r="D10" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="E10" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="I9" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="36" t="s">
+      <c r="F10" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="K9" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="38" t="s">
+      <c r="H10" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="M9" s="38" t="s">
+      <c r="I10" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="N9" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O9" s="38" t="s">
+      <c r="K10" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="P9" s="39" t="s">
+      <c r="M10" s="38" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="10" ht="116.25" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="N10" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="P10" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="33" t="s">
+    </row>
+    <row r="11" ht="116.25" customHeight="1">
+      <c r="A11" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="B11" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="36" t="s">
+      <c r="D11" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="E11" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="I10" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="36" t="s">
+      <c r="F11" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="K10" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="38" t="s">
+      <c r="H11" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="M10" s="38" t="s">
+      <c r="I11" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="N10" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O10" s="38" t="s">
+      <c r="K11" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="P10" s="39" t="s">
+      <c r="M11" s="38" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="11" ht="116.25" customHeight="1">
-      <c r="A11" s="31" t="s">
+      <c r="N11" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="P11" s="39" t="s">
         <v>159</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="K11" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="M11" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="N11" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="O11" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="P11" s="39" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="12" ht="116.25" customHeight="1">
       <c r="A12" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="K12" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="M12" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="N12" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" s="47" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="P12" s="48" t="s">
         <v>171</v>
       </c>
-      <c r="C12" s="44" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="I12" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="46" t="s">
-        <v>177</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="M12" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="N12" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="O12" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="P12" s="48" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="13">
-      <c r="F13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="F13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14">
-      <c r="F14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15">
-      <c r="F15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="F15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16">
-      <c r="F16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="F16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="17">
-      <c r="F17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="F17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="F18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="F18" s="2"/>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="F19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="F19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="F20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="F20" s="2"/>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="F21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="F21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="F22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="F22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="F23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="F23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="F24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="F24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="F25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="F25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="F26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="F27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="F27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="F28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="K28" s="2"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="F29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="F29" s="2"/>
+      <c r="K29" s="2"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="F30" s="1"/>
-      <c r="K30" s="1"/>
+      <c r="F30" s="2"/>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="F31" s="1"/>
-      <c r="K31" s="1"/>
+      <c r="F31" s="2"/>
+      <c r="K31" s="2"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="F32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="F32" s="2"/>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="F33" s="1"/>
-      <c r="K33" s="1"/>
+      <c r="F33" s="2"/>
+      <c r="K33" s="2"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="F34" s="1"/>
-      <c r="K34" s="1"/>
+      <c r="F34" s="2"/>
+      <c r="K34" s="2"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="F35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="F35" s="2"/>
+      <c r="K35" s="2"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="F36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="F36" s="2"/>
+      <c r="K36" s="2"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="F37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="F37" s="2"/>
+      <c r="K37" s="2"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="F38" s="1"/>
-      <c r="K38" s="1"/>
+      <c r="F38" s="2"/>
+      <c r="K38" s="2"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="F39" s="1"/>
-      <c r="K39" s="1"/>
+      <c r="F39" s="2"/>
+      <c r="K39" s="2"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="F40" s="1"/>
-      <c r="K40" s="1"/>
+      <c r="F40" s="2"/>
+      <c r="K40" s="2"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="F41" s="1"/>
-      <c r="K41" s="1"/>
+      <c r="F41" s="2"/>
+      <c r="K41" s="2"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="F42" s="1"/>
-      <c r="K42" s="1"/>
+      <c r="F42" s="2"/>
+      <c r="K42" s="2"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="F43" s="1"/>
-      <c r="K43" s="1"/>
+      <c r="F43" s="2"/>
+      <c r="K43" s="2"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="F44" s="1"/>
-      <c r="K44" s="1"/>
+      <c r="F44" s="2"/>
+      <c r="K44" s="2"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="F45" s="1"/>
-      <c r="K45" s="1"/>
+      <c r="F45" s="2"/>
+      <c r="K45" s="2"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="F46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="F46" s="2"/>
+      <c r="K46" s="2"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="F47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="F47" s="2"/>
+      <c r="K47" s="2"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
@@ -3928,20 +3898,16 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="21.13"/>
     <col customWidth="1" min="2" max="2" width="68.88"/>
-    <col customWidth="1" min="3" max="3" width="45.5"/>
-    <col customWidth="1" min="4" max="4" width="34.5"/>
-    <col customWidth="1" min="5" max="6" width="8.63"/>
+    <col customWidth="1" min="3" max="4" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="1">
@@ -3950,10 +3916,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
       <c r="A5" s="8" t="s">
@@ -3962,154 +3926,106 @@
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8" t="s">
+    </row>
+    <row r="6" ht="58.5" customHeight="1">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="58.5" customHeight="1">
-      <c r="A6" s="11" t="s">
+    <row r="7" ht="58.5" customHeight="1">
+      <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="B7" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="58.5" customHeight="1">
+      <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" ht="58.5" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="B8" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="58.5" customHeight="1">
+      <c r="A9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="B9" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" ht="58.5" customHeight="1">
-      <c r="A8" s="14" t="s">
+    </row>
+    <row r="10">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" ht="21.0" customHeight="1">
+      <c r="A11" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" ht="46.5" customHeight="1">
+      <c r="A12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B12" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="16" t="s">
+    </row>
+    <row r="13" ht="46.5" customHeight="1">
+      <c r="A13" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="B13" s="24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" ht="58.5" customHeight="1">
-      <c r="A9" s="20" t="s">
+    <row r="14" ht="46.5" customHeight="1">
+      <c r="A14" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B14" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="21" t="s">
+    </row>
+    <row r="15" ht="46.5" customHeight="1">
+      <c r="A15" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="B15" s="24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" ht="21.0" customHeight="1">
-      <c r="A11" s="25" t="s">
+    <row r="16" ht="46.5" customHeight="1">
+      <c r="A16" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="25" t="s">
+    </row>
+    <row r="17" ht="46.5" customHeight="1">
+      <c r="A17" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" ht="46.5" customHeight="1">
-      <c r="A12" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" ht="46.5" customHeight="1">
-      <c r="A13" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" ht="46.5" customHeight="1">
-      <c r="A15" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" ht="46.5" customHeight="1">
-      <c r="A16" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" ht="46.5" customHeight="1">
-      <c r="A17" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
     </row>
     <row r="18" ht="46.5" customHeight="1">
-      <c r="A18" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -5093,8 +5009,8 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
